--- a/output/graficos_envejecimiento/plot_regional_d_enveje_a_2024_maule_provincial.xlsx
+++ b/output/graficos_envejecimiento/plot_regional_d_enveje_a_2024_maule_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 23:49</t>
+    <t xml:space="preserve">2026-10-05 05:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
